--- a/Teoría de la información/Práctica Exámen MC.xlsx
+++ b/Teoría de la información/Práctica Exámen MC.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D2BC40-DBA3-4EC8-A750-7C5EAAFD71B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEE8B04-D1A8-4D54-BC0C-35B22AE58C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{1B2D5A58-B732-405D-921E-4B9C3DD4EFC9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Canales" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
   <si>
     <t>a</t>
   </si>
@@ -63,22 +63,13 @@
     <t>Frecuencia de salida</t>
   </si>
   <si>
-    <t>Autoinformación:</t>
-  </si>
-  <si>
     <t>Voy a poner otra letra (e) para rellenar</t>
   </si>
   <si>
-    <t>Revisen la autoinformación porfa no sé si la estoy sacando de los datos correctos</t>
-  </si>
-  <si>
     <t>Entropía</t>
   </si>
   <si>
-    <t>Por Si las dudas, haré 2 tablas de entropía no sé cúal sea correcta</t>
-  </si>
-  <si>
-    <t>Qué</t>
+    <t>Información mutua</t>
   </si>
 </sst>
 </file>
@@ -86,9 +77,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,8 +101,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -136,12 +135,29 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor theme="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -150,36 +166,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="173" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -197,16 +225,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}" name="Tabla2" displayName="Tabla2" ref="B3:G5" totalsRowShown="0">
-  <autoFilter ref="B3:G5" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{558271E2-8147-4FF6-A576-81B8AE3DC0C6}" name="Columna1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}" name="Tabla2" displayName="Tabla2" ref="B3:H5" totalsRowShown="0">
+  <autoFilter ref="B3:H5" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{558271E2-8147-4FF6-A576-81B8AE3DC0C6}" name="Columna1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{9606F360-3E10-49C1-927F-5CE7FBF5E527}" name="a"/>
     <tableColumn id="3" xr3:uid="{6073D23E-82CB-4AB8-A44D-081765527F15}" name="b"/>
     <tableColumn id="4" xr3:uid="{995500E9-C3ED-443B-9E33-D34E0EA48033}" name="c"/>
     <tableColumn id="5" xr3:uid="{AC632472-55EC-4F2C-A210-966C886E61BA}" name="d"/>
     <tableColumn id="6" xr3:uid="{8E4CED38-6B50-4742-BA8B-8089089769D1}" name="Suma">
       <calculatedColumnFormula>SUM(C4:F5)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{5C57A484-68FF-4E7D-890A-EE2B34EE8552}" name="Probabilidad de fallo" dataDxfId="0">
+      <calculatedColumnFormula xml:space="preserve"> 1 - 0.95</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -510,13 +541,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F4CD5B-2086-42F8-A12B-876693EB4F9D}">
-  <dimension ref="A3:N21"/>
+  <dimension ref="A3:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -535,11 +568,11 @@
       <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H3" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -559,30 +592,40 @@
         <f>CONCATENATE(SUM(C4:F5), " , debería ser 1")</f>
         <v>0.8 , debería ser 1</v>
       </c>
-      <c r="I4">
-        <f xml:space="preserve"> 1 - 0.95</f>
+      <c r="H4" s="12">
+        <f t="shared" ref="H4:H5" si="0" xml:space="preserve"> 1 - 0.95</f>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
       <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="I6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2"/>
@@ -601,8 +644,10 @@
       <c r="G7" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I7" s="14"/>
+      <c r="J7" s="15"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>0.17</v>
       </c>
@@ -617,20 +662,28 @@
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" ref="C8:G12" si="0">(1 - $C$8) / 4</f>
+        <f t="shared" ref="C8:G12" si="1">(1 - $C$8) / 4</f>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="F8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000011E-2</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="4">
+        <f>-LOG(C8, 2)</f>
+        <v>7.4000581443776928E-2</v>
+      </c>
+      <c r="J8" s="3">
+        <f>I8 * C8</f>
+        <v>7.0300552371588082E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>0.38</v>
       </c>
@@ -638,26 +691,34 @@
         <v>1</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="D9" s="4">
         <v>0.95</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="F9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000011E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <f t="shared" ref="I9:I12" si="2">-LOG(C9, 2)</f>
+        <v>6.3219280948873608</v>
+      </c>
+      <c r="J9" s="3">
+        <f t="shared" ref="J9:J12" si="3">I9 * C9</f>
+        <v>7.9024101186092086E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>0.2</v>
       </c>
@@ -665,26 +726,34 @@
         <v>2</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="D10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="E10" s="4">
         <v>0.95</v>
       </c>
       <c r="F10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000011E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <f t="shared" si="2"/>
+        <v>6.3219280948873608</v>
+      </c>
+      <c r="J10" s="3">
+        <f t="shared" si="3"/>
+        <v>7.9024101186092086E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>0.05</v>
       </c>
@@ -692,26 +761,34 @@
         <v>3</v>
       </c>
       <c r="C11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="F11" s="4">
         <v>0.95</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <f t="shared" si="1"/>
+        <v>1.2500000000000011E-2</v>
+      </c>
+      <c r="I11" s="4">
+        <f t="shared" si="2"/>
+        <v>6.3219280948873608</v>
+      </c>
+      <c r="J11" s="3">
+        <f t="shared" si="3"/>
+        <v>7.9024101186092086E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>0.2</v>
       </c>
@@ -719,51 +796,55 @@
         <v>8</v>
       </c>
       <c r="C12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="D12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.2500000000000011E-2</v>
       </c>
       <c r="G12" s="4">
         <v>0.95</v>
       </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="M13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13" s="8"/>
-    </row>
-    <row r="14" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="5" t="s">
+      <c r="H12" s="6"/>
+      <c r="I12" s="4">
+        <f t="shared" si="2"/>
+        <v>6.3219280948873608</v>
+      </c>
+      <c r="J12" s="3">
+        <f t="shared" si="3"/>
+        <v>7.9024101186092086E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I13" s="9">
+        <f>SUM(I8:I12)</f>
+        <v>25.36171296099322</v>
+      </c>
+      <c r="J13" s="5">
+        <f>SUM(J8:J12)</f>
+        <v>0.38639695711595645</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>0</v>
@@ -780,18 +861,8 @@
       <c r="G15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>0</v>
       </c>
@@ -804,218 +875,150 @@
         <v>2.1250000000000019E-3</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" ref="E16:G16" si="1">E8 * $A8</f>
+        <f t="shared" ref="E16:G16" si="4">E8 * $A8</f>
         <v>2.1250000000000019E-3</v>
       </c>
       <c r="F16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.1250000000000019E-3</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.1250000000000019E-3</v>
       </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="11">
-        <f>C21</f>
-        <v>0.171875</v>
-      </c>
-      <c r="J16" s="2">
-        <f>-LOG(I16,2)</f>
-        <v>2.5405683813627027</v>
-      </c>
-      <c r="K16" s="2">
-        <f>J16 * I16</f>
-        <v>0.43666019054671451</v>
-      </c>
-      <c r="M16" s="2">
-        <f>(-LOG(C8, 2) * C8) - 3*(F8 * LOG(F8,2))</f>
-        <v>0.3073728559298643</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" ref="C17:G20" si="2">C9 * $A9</f>
+        <f t="shared" ref="C17:G20" si="5">C9 * $A9</f>
         <v>4.7500000000000042E-3</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.36099999999999999</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.7500000000000042E-3</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.7500000000000042E-3</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.7500000000000042E-3</v>
       </c>
-      <c r="I17" s="11">
-        <f>D21</f>
-        <v>0.36874999999999997</v>
-      </c>
-      <c r="J17" s="2">
-        <f t="shared" ref="J17:J20" si="3">-LOG(I17,2)</f>
-        <v>1.4392850455255213</v>
-      </c>
-      <c r="K17" s="2">
-        <f t="shared" ref="K17:K20" si="4">J17 * I17</f>
-        <v>0.53073636053753592</v>
-      </c>
-      <c r="M17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
-      <c r="I18" s="11">
-        <f>E21</f>
-        <v>0.2</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="3"/>
-        <v>2.3219280948873622</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="4"/>
-        <v>0.46438561897747244</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2500000000000056E-4</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2500000000000056E-4</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2500000000000056E-4</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>4.7500000000000001E-2</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6.2500000000000056E-4</v>
       </c>
-      <c r="I19" s="11">
-        <f>F21</f>
-        <v>5.9375000000000011E-2</v>
-      </c>
-      <c r="J19" s="2">
-        <f t="shared" si="3"/>
-        <v>4.0740005814437765</v>
-      </c>
-      <c r="K19" s="2">
-        <f t="shared" si="4"/>
-        <v>0.24189378452322427</v>
-      </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="F20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2.5000000000000022E-3</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0.19</v>
       </c>
-      <c r="I20" s="11">
-        <f>G21</f>
-        <v>0.2</v>
-      </c>
-      <c r="J20" s="2">
-        <f t="shared" si="3"/>
-        <v>2.3219280948873622</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="4"/>
-        <v>0.46438561897747244</v>
-      </c>
-    </row>
-    <row r="21" spans="2:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="10" t="s">
+    </row>
+    <row r="21" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="10">
         <f>SUM(C16:C20)</f>
         <v>0.171875</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <f>SUM(D16:D20)</f>
         <v>0.36874999999999997</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="10">
         <f>SUM(E16:E20)</f>
         <v>0.2</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="10">
         <f>SUM(F16:F20)</f>
         <v>5.9375000000000011E-2</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="10">
         <f>SUM(G16:G20)</f>
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M13:N14"/>
+  <mergeCells count="4">
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="B14:G14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I13:J14"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Teoría de la información/Práctica Exámen MC.xlsx
+++ b/Teoría de la información/Práctica Exámen MC.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal del laboratorio\1924910\Tareas\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BEE8B04-D1A8-4D54-BC0C-35B22AE58C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" xr2:uid="{1B2D5A58-B732-405D-921E-4B9C3DD4EFC9}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20370" windowHeight="12210" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Canales" sheetId="1" r:id="rId1"/>
+    <sheet name="Árbol jerarquico" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>a</t>
   </si>
@@ -70,12 +70,69 @@
   </si>
   <si>
     <t>Información mutua</t>
+  </si>
+  <si>
+    <t>Una corona di spine</t>
+  </si>
+  <si>
+    <t>Sarà il dress-code per la mia festa</t>
+  </si>
+  <si>
+    <t>Contamos cada letra</t>
+  </si>
+  <si>
+    <t>à</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>"-"</t>
+  </si>
+  <si>
+    <t>Letra</t>
+  </si>
+  <si>
+    <t>Frecuencia abs</t>
+  </si>
+  <si>
+    <t>Freciemcoa rel</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
@@ -184,14 +241,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -225,18 +282,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}" name="Tabla2" displayName="Tabla2" ref="B3:H5" totalsRowShown="0">
-  <autoFilter ref="B3:H5" xr:uid="{797F4F2A-DE83-4A93-A720-F635F352A5C7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="B3:H5" totalsRowShown="0">
+  <autoFilter ref="B3:H5"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{558271E2-8147-4FF6-A576-81B8AE3DC0C6}" name="Columna1" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{9606F360-3E10-49C1-927F-5CE7FBF5E527}" name="a"/>
-    <tableColumn id="3" xr3:uid="{6073D23E-82CB-4AB8-A44D-081765527F15}" name="b"/>
-    <tableColumn id="4" xr3:uid="{995500E9-C3ED-443B-9E33-D34E0EA48033}" name="c"/>
-    <tableColumn id="5" xr3:uid="{AC632472-55EC-4F2C-A210-966C886E61BA}" name="d"/>
-    <tableColumn id="6" xr3:uid="{8E4CED38-6B50-4742-BA8B-8089089769D1}" name="Suma">
+    <tableColumn id="1" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="2" name="a"/>
+    <tableColumn id="3" name="b"/>
+    <tableColumn id="4" name="c"/>
+    <tableColumn id="5" name="d"/>
+    <tableColumn id="6" name="Suma">
       <calculatedColumnFormula>SUM(C4:F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{5C57A484-68FF-4E7D-890A-EE2B34EE8552}" name="Probabilidad de fallo" dataDxfId="0">
+    <tableColumn id="7" name="Probabilidad de fallo" dataDxfId="0">
       <calculatedColumnFormula xml:space="preserve"> 1 - 0.95</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -540,16 +597,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F4CD5B-2086-42F8-A12B-876693EB4F9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -568,11 +625,11 @@
       <c r="G3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
@@ -592,12 +649,12 @@
         <f>CONCATENATE(SUM(C4:F5), " , debería ser 1")</f>
         <v>0.8 , debería ser 1</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <f t="shared" ref="H4:H5" si="0" xml:space="preserve"> 1 - 0.95</f>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="G5" s="1" t="s">
         <v>12</v>
@@ -607,16 +664,16 @@
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
       <c r="I6" s="14" t="s">
         <v>14</v>
       </c>
@@ -624,7 +681,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
@@ -647,7 +704,7 @@
       <c r="I7" s="14"/>
       <c r="J7" s="15"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>0.17</v>
       </c>
@@ -683,7 +740,7 @@
         <v>7.0300552371588082E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>0.38</v>
       </c>
@@ -718,7 +775,7 @@
         <v>7.9024101186092086E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>0.2</v>
       </c>
@@ -753,7 +810,7 @@
         <v>7.9024101186092086E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>0.05</v>
       </c>
@@ -788,7 +845,7 @@
         <v>7.9024101186092086E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>0.2</v>
       </c>
@@ -824,7 +881,7 @@
         <v>7.9024101186092086E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I13" s="9">
         <f>SUM(I8:I12)</f>
         <v>25.36171296099322</v>
@@ -834,17 +891,17 @@
         <v>0.38639695711595645</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
+    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>0</v>
@@ -862,7 +919,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>0</v>
       </c>
@@ -888,7 +945,7 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
@@ -913,7 +970,7 @@
         <v>4.7500000000000042E-3</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
@@ -938,7 +995,7 @@
         <v>2.5000000000000022E-3</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
@@ -963,7 +1020,7 @@
         <v>6.2500000000000056E-4</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>8</v>
       </c>
@@ -988,7 +1045,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
         <v>11</v>
       </c>
@@ -1026,4 +1083,329 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <f>C6 / $C$23</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="E6">
+        <f>-LOG(D6, 2) * D6</f>
+        <v>0.3875854127478025</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D22" si="0">C7 / $C$23</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7:E22" si="1">-LOG(D7, 2) * D7</f>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0.19963791539243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0.26045937304056793</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>0.3522138890491458</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0.31038694189597116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>0.19963791539243</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>0.26045937304056793</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>0.26045937304056793</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>0.19963791539243</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>8.8888888888888892E-2</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="1"/>
+        <v>0.31038694189597116</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="1"/>
+        <v>0.3522138890491458</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="1"/>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="1"/>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>0.12204117991843723</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <f>SUM(C6:C22)</f>
+        <v>45</v>
+      </c>
+      <c r="E23">
+        <f>SUM(E6:E22)</f>
+        <v>3.8253260194476537</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Teoría de la información/Práctica Exámen MC.xlsx
+++ b/Teoría de la información/Práctica Exámen MC.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal del laboratorio\1924910\Tareas\Teoría de la información\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\Repositorios\Semestre-EneJun2026\Teoría de la información\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D0E518-89A6-46E1-816E-84A888B9C9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20370" windowHeight="12210" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="20376" windowHeight="12216" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Canales" sheetId="1" r:id="rId1"/>
     <sheet name="Árbol jerarquico" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>a</t>
   </si>
@@ -39,9 +40,6 @@
     <t>d</t>
   </si>
   <si>
-    <t>Suma</t>
-  </si>
-  <si>
     <t>Probabilidad de aparición</t>
   </si>
   <si>
@@ -51,9 +49,6 @@
     <t>Probabilidad de fallo</t>
   </si>
   <si>
-    <t>e</t>
-  </si>
-  <si>
     <t>Matríz de Trancisción</t>
   </si>
   <si>
@@ -63,80 +58,101 @@
     <t>Frecuencia de salida</t>
   </si>
   <si>
-    <t>Voy a poner otra letra (e) para rellenar</t>
-  </si>
-  <si>
     <t>Entropía</t>
   </si>
   <si>
     <t>Información mutua</t>
   </si>
   <si>
-    <t>Una corona di spine</t>
-  </si>
-  <si>
-    <t>Sarà il dress-code per la mia festa</t>
-  </si>
-  <si>
     <t>Contamos cada letra</t>
   </si>
   <si>
-    <t>à</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>i</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>o</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>"-"</t>
-  </si>
-  <si>
     <t>Letra</t>
   </si>
   <si>
-    <t>Frecuencia abs</t>
-  </si>
-  <si>
-    <t>Freciemcoa rel</t>
+    <t>Matrícula:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">b             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">d             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">e            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">h             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">i             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">j            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">k             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">l            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">m            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">n            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">o            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">p            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">r             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">s            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">t             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">u             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">v            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">y             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ä            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ö             </t>
+  </si>
+  <si>
+    <t>Frec Abs</t>
+  </si>
+  <si>
+    <t>Frec Rel</t>
+  </si>
+  <si>
+    <t>&lt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +178,20 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -199,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -218,12 +248,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -241,11 +286,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -256,12 +304,30 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -282,19 +348,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabla2" displayName="Tabla2" ref="B3:H5" totalsRowShown="0">
-  <autoFilter ref="B3:H5"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Columna1" dataDxfId="1"/>
-    <tableColumn id="2" name="a"/>
-    <tableColumn id="3" name="b"/>
-    <tableColumn id="4" name="c"/>
-    <tableColumn id="5" name="d"/>
-    <tableColumn id="6" name="Suma">
-      <calculatedColumnFormula>SUM(C4:F5)</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla2" displayName="Tabla2" ref="B3:G4" totalsRowShown="0">
+  <autoFilter ref="B3:G4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Columna1" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="a"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="b"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="c"/>
+    <tableColumn id="10" xr3:uid="{C15278ED-9D04-463F-9ADF-389D6195D55A}" name="d" dataDxfId="0">
+      <calculatedColumnFormula>A12</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="Probabilidad de fallo" dataDxfId="0">
-      <calculatedColumnFormula xml:space="preserve"> 1 - 0.95</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Probabilidad de fallo" dataDxfId="1">
+      <calculatedColumnFormula xml:space="preserve"> 1 - 0.98</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -597,18 +662,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:J21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="66.599999999999994" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B1" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="18">
+        <v>1</v>
+      </c>
+      <c r="D1" s="18">
+        <v>9</v>
+      </c>
+      <c r="E1" s="18">
+        <v>2</v>
+      </c>
+      <c r="F1" s="18">
+        <v>4</v>
+      </c>
+      <c r="G1" s="19">
+        <v>9</v>
+      </c>
+      <c r="H1" s="19">
+        <v>1</v>
+      </c>
+      <c r="I1" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -622,16 +714,13 @@
       <c r="F3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C4">
         <v>0.17</v>
@@ -643,265 +732,202 @@
         <v>0.2</v>
       </c>
       <c r="F4">
-        <v>0.05</v>
-      </c>
-      <c r="G4" s="1" t="str">
-        <f>CONCATENATE(SUM(C4:F5), " , debería ser 1")</f>
-        <v>0.8 , debería ser 1</v>
-      </c>
-      <c r="H4" s="11">
-        <f t="shared" ref="H4:H5" si="0" xml:space="preserve"> 1 - 0.95</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
+        <f>A12</f>
+        <v>0.25</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" ref="G4" si="0" xml:space="preserve"> 1 - 0.98</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="I6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="1"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="13"/>
+      <c r="H7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F8" s="2"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>0.17</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="D9" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="E9" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="F9" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="G9" s="6"/>
+      <c r="H9" s="4">
+        <f>-LOG(C9, 2)</f>
+        <v>2.9146345659516508E-2</v>
+      </c>
+      <c r="I9" s="3">
+        <f>H9 * C9</f>
+        <v>2.8563418746326178E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <v>0.38</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="E10" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="F10" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="H10" s="4">
+        <f>-LOG(C10, 2)</f>
+        <v>7.2288186904958796</v>
+      </c>
+      <c r="I10" s="3">
+        <f>H10 * C10</f>
+        <v>4.8192124603305901E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="D11" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="F11" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="H11" s="4">
+        <f>-LOG(C11, 2)</f>
+        <v>7.2288186904958796</v>
+      </c>
+      <c r="I11" s="3">
+        <f>H11 * C11</f>
+        <v>4.8192124603305901E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f>1 - (SUM(A9:A11))</f>
+        <v>0.25</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="C12" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="D12" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="E12" s="4">
+        <f>(1 - $C$9) / 3</f>
+        <v>6.6666666666666723E-3</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.98</v>
+      </c>
+      <c r="H12" s="4">
+        <f>-LOG(C12, 2)</f>
+        <v>7.2288186904958796</v>
+      </c>
+      <c r="I12" s="3">
+        <f>H12 * C12</f>
+        <v>4.8192124603305901E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="9">
+        <f>SUM(H9:H11)</f>
+        <v>14.486783726651275</v>
+      </c>
+      <c r="I13" s="5">
+        <f>SUM(I9:I12)</f>
+        <v>0.1731397925562439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <v>0.17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="D8" s="4">
-        <f>(1 - $C$8) / 4</f>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" ref="C8:G12" si="1">(1 - $C$8) / 4</f>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="F8" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="4">
-        <f>-LOG(C8, 2)</f>
-        <v>7.4000581443776928E-2</v>
-      </c>
-      <c r="J8" s="3">
-        <f>I8 * C8</f>
-        <v>7.0300552371588082E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>0.38</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="F9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" ref="I9:I12" si="2">-LOG(C9, 2)</f>
-        <v>6.3219280948873608</v>
-      </c>
-      <c r="J9" s="3">
-        <f t="shared" ref="J9:J12" si="3">I9 * C9</f>
-        <v>7.9024101186092086E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="D10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="F10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="G10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="2"/>
-        <v>6.3219280948873608</v>
-      </c>
-      <c r="J10" s="3">
-        <f t="shared" si="3"/>
-        <v>7.9024101186092086E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="D11" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="E11" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="G11" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="2"/>
-        <v>6.3219280948873608</v>
-      </c>
-      <c r="J11" s="3">
-        <f t="shared" si="3"/>
-        <v>7.9024101186092086E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="D12" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="E12" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="F12" s="4">
-        <f t="shared" si="1"/>
-        <v>1.2500000000000011E-2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.95</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="4">
-        <f t="shared" si="2"/>
-        <v>6.3219280948873608</v>
-      </c>
-      <c r="J12" s="3">
-        <f t="shared" si="3"/>
-        <v>7.9024101186092086E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I13" s="9">
-        <f>SUM(I8:I12)</f>
-        <v>25.36171296099322</v>
-      </c>
-      <c r="J13" s="5">
-        <f>SUM(J8:J12)</f>
-        <v>0.38639695711595645</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
         <v>0</v>
@@ -915,167 +941,118 @@
       <c r="F15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="4">
-        <f>C8 * $A8</f>
-        <v>0.1615</v>
+        <f>C9 * $A9</f>
+        <v>0.1666</v>
       </c>
       <c r="D16" s="4">
-        <f>D8 * $A8</f>
-        <v>2.1250000000000019E-3</v>
+        <f>D9 * $A9</f>
+        <v>1.1333333333333343E-3</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" ref="E16:G16" si="4">E8 * $A8</f>
-        <v>2.1250000000000019E-3</v>
-      </c>
-      <c r="F16" s="4">
-        <f t="shared" si="4"/>
-        <v>2.1250000000000019E-3</v>
-      </c>
-      <c r="G16" s="4">
-        <f t="shared" si="4"/>
-        <v>2.1250000000000019E-3</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+        <f>E9 * $A9</f>
+        <v>1.1333333333333343E-3</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="4">
-        <f t="shared" ref="C17:G20" si="5">C9 * $A9</f>
-        <v>4.7500000000000042E-3</v>
+        <f>C10 * $A10</f>
+        <v>2.5333333333333354E-3</v>
       </c>
       <c r="D17" s="4">
-        <f t="shared" si="5"/>
-        <v>0.36099999999999999</v>
+        <f>D10 * $A10</f>
+        <v>0.37240000000000001</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="5"/>
-        <v>4.7500000000000042E-3</v>
+        <f>E10 * $A10</f>
+        <v>2.5333333333333354E-3</v>
       </c>
       <c r="F17" s="4">
-        <f t="shared" si="5"/>
-        <v>4.7500000000000042E-3</v>
-      </c>
-      <c r="G17" s="4">
-        <f t="shared" si="5"/>
-        <v>4.7500000000000042E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+        <f>F10 * $A10</f>
+        <v>2.5333333333333354E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
+        <f>C11 * $A11</f>
+        <v>1.3333333333333346E-3</v>
       </c>
       <c r="D18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
+        <f>D11 * $A11</f>
+        <v>1.3333333333333346E-3</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="5"/>
-        <v>0.19</v>
+        <f>E11 * $A11</f>
+        <v>0.19600000000000001</v>
       </c>
       <c r="F18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-      <c r="G18" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <f>F11 * $A11</f>
+        <v>1.3333333333333346E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="4">
-        <f t="shared" si="5"/>
-        <v>6.2500000000000056E-4</v>
+        <f>C12 * $A12</f>
+        <v>1.6666666666666681E-3</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" si="5"/>
-        <v>6.2500000000000056E-4</v>
+        <f>D12 * $A12</f>
+        <v>1.6666666666666681E-3</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="5"/>
-        <v>6.2500000000000056E-4</v>
+        <f>E12 * $A12</f>
+        <v>1.6666666666666681E-3</v>
       </c>
       <c r="F19" s="4">
-        <f t="shared" si="5"/>
-        <v>4.7500000000000001E-2</v>
-      </c>
-      <c r="G19" s="4">
-        <f t="shared" si="5"/>
-        <v>6.2500000000000056E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-      <c r="D20" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-      <c r="E20" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-      <c r="F20" s="4">
-        <f t="shared" si="5"/>
-        <v>2.5000000000000022E-3</v>
-      </c>
-      <c r="G20" s="4">
-        <f t="shared" si="5"/>
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B21" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="10">
-        <f>SUM(C16:C20)</f>
-        <v>0.171875</v>
-      </c>
-      <c r="D21" s="10">
-        <f>SUM(D16:D20)</f>
-        <v>0.36874999999999997</v>
-      </c>
-      <c r="E21" s="10">
-        <f>SUM(E16:E20)</f>
-        <v>0.2</v>
-      </c>
-      <c r="F21" s="10">
-        <f>SUM(F16:F20)</f>
-        <v>5.9375000000000011E-2</v>
-      </c>
-      <c r="G21" s="10">
-        <f>SUM(G16:G20)</f>
-        <v>0.2</v>
+        <f>F12 * $A12</f>
+        <v>0.245</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="10">
+        <f>SUM(C16:C18)</f>
+        <v>0.17046666666666666</v>
+      </c>
+      <c r="D20" s="10">
+        <f>SUM(D16:D18)</f>
+        <v>0.37486666666666668</v>
+      </c>
+      <c r="E20" s="10">
+        <f>SUM(E16:E18)</f>
+        <v>0.19966666666666669</v>
+      </c>
+      <c r="F20" s="10">
+        <f>SUM(F16:F18)</f>
+        <v>3.8666666666666702E-3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B14:G14"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1086,326 +1063,386 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B4:E28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" customWidth="1"/>
     <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
       <c r="C6">
-        <v>6</v>
+        <v>59928</v>
       </c>
       <c r="D6">
-        <f>C6 / $C$23</f>
-        <v>0.13333333333333333</v>
+        <f>C6 / $C$27</f>
+        <v>3.2144730673629711E-2</v>
       </c>
       <c r="E6">
         <f>-LOG(D6, 2) * D6</f>
-        <v>0.3875854127478025</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.15941452471011275</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>59929</v>
+      </c>
+      <c r="D7">
+        <f>C7 / $C$27</f>
+        <v>3.2145267062807951E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7:E28" si="0">-LOG(D7, 2) * D7</f>
+        <v>0.15941641095851508</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>60316</v>
+      </c>
+      <c r="D8">
+        <f>C8 / $C$27</f>
+        <v>3.2352849674787243E-2</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0.16014542170424115</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <f t="shared" ref="D7:D22" si="0">C7 / $C$23</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ref="E7:E22" si="1">-LOG(D7, 2) * D7</f>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>4.4444444444444446E-2</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>0.19963791539243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
       <c r="C9">
-        <v>3</v>
+        <v>120814</v>
       </c>
       <c r="D9">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <f>C9 / $C$27</f>
+        <v>6.4803322180014347E-2</v>
       </c>
       <c r="E9">
-        <f t="shared" si="1"/>
-        <v>0.26045937304056793</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25582980450187676</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>60025</v>
       </c>
       <c r="D10">
-        <f t="shared" si="0"/>
-        <v>0.1111111111111111</v>
+        <f>C10 / $C$27</f>
+        <v>3.2196760423919092E-2</v>
       </c>
       <c r="E10">
-        <f t="shared" si="1"/>
-        <v>0.3522138890491458</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15959743071528915</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>60033</v>
       </c>
       <c r="D11">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <f>C11 / $C$27</f>
+        <v>3.2201051537345024E-2</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15961251032929963</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>120317</v>
       </c>
       <c r="D12">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888892E-2</v>
+        <f>C12 / $C$27</f>
+        <v>6.4536736758428553E-2</v>
       </c>
       <c r="E12">
-        <f t="shared" si="1"/>
-        <v>0.31038694189597116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25516119096246176</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>60137</v>
       </c>
       <c r="D13">
-        <f t="shared" si="0"/>
-        <v>4.4444444444444446E-2</v>
+        <f>C13 / $C$27</f>
+        <v>3.2256836011882097E-2</v>
       </c>
       <c r="E13">
-        <f t="shared" si="1"/>
-        <v>0.19963791539243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15980847027805622</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>120309</v>
       </c>
       <c r="D14">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <f>C14 / $C$27</f>
+        <v>6.4532445645002628E-2</v>
       </c>
       <c r="E14">
-        <f t="shared" si="1"/>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25515041559696305</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>119627</v>
       </c>
       <c r="D15">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <f>C15 / $C$27</f>
+        <v>6.4166628225442224E-2</v>
       </c>
       <c r="E15">
-        <f t="shared" si="1"/>
-        <v>0.26045937304056793</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25423029943247633</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>120048</v>
       </c>
       <c r="D16">
-        <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <f>C16 / $C$27</f>
+        <v>6.4392448069481703E-2</v>
       </c>
       <c r="E16">
-        <f t="shared" si="1"/>
-        <v>0.26045937304056793</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25479864334156987</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>120748</v>
       </c>
       <c r="D17">
-        <f t="shared" si="0"/>
-        <v>4.4444444444444446E-2</v>
+        <f>C17 / $C$27</f>
+        <v>6.4767920494250439E-2</v>
       </c>
       <c r="E17">
-        <f t="shared" si="1"/>
-        <v>0.19963791539243</v>
-      </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25574110602025257</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>120423</v>
       </c>
       <c r="D18">
-        <f t="shared" si="0"/>
-        <v>8.8888888888888892E-2</v>
+        <f>C18 / $C$27</f>
+        <v>6.45935940113221E-2</v>
       </c>
       <c r="E18">
-        <f t="shared" si="1"/>
-        <v>0.31038694189597116</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.2553039257053758</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>5</v>
+        <v>59921</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
-        <v>0.1111111111111111</v>
+        <f>C19 / $C$27</f>
+        <v>3.2140975949382027E-2</v>
       </c>
       <c r="E19">
-        <f t="shared" si="1"/>
-        <v>0.3522138890491458</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15940132060972226</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>120108</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <f>C20 / $C$27</f>
+        <v>6.4424631420176168E-2</v>
       </c>
       <c r="E20">
-        <f t="shared" si="1"/>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.25487954936232532</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>60041</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <f>C21 / $C$27</f>
+        <v>3.2205342650770949E-2</v>
       </c>
       <c r="E21">
-        <f t="shared" si="1"/>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15962758911832811</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>60115</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <f>C22 / $C$27</f>
+        <v>3.2245035449960789E-2</v>
       </c>
       <c r="E22">
-        <f t="shared" si="1"/>
-        <v>0.12204117991843723</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>0.15976702882706911</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
       <c r="C23">
-        <f>SUM(C6:C22)</f>
-        <v>45</v>
+        <v>120168</v>
+      </c>
+      <c r="D23">
+        <f>C23 / $C$27</f>
+        <v>6.4456814770870632E-2</v>
       </c>
       <c r="E23">
-        <f>SUM(E6:E22)</f>
-        <v>3.8253260194476537</v>
+        <f t="shared" si="0"/>
+        <v>0.25496043218857467</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24">
+        <v>59955</v>
+      </c>
+      <c r="D24">
+        <f>C24 / $C$27</f>
+        <v>3.2159213181442221E-2</v>
+      </c>
+      <c r="E24">
+        <f>-LOG(D24, 2) * D24</f>
+        <v>0.15946544888524372</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>121127</v>
+      </c>
+      <c r="D25">
+        <f>C25 / $C$27</f>
+        <v>6.4971211992803798E-2</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>0.25625007067111033</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26">
+        <v>60229</v>
+      </c>
+      <c r="D26">
+        <f>C26 / $C$27</f>
+        <v>3.2306183816280268E-2</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>0.15998170343737436</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <f>SUM(C6:C26)</f>
+        <v>1864318</v>
+      </c>
+      <c r="E27">
+        <f>SUM(E6:E26)</f>
+        <v>4.3085432973562376</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E28" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>